--- a/out/LSTM-mamba2_repeat_5_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.204705233669806</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.804705233669806</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.713175878173206e-05</v>
+        <v>-9.028927320521324e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08860957632026108</v>
+        <v>-0.1037250332593648</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.0888193256065232</v>
+        <v>-0.1038953169789104</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4768624264230748</v>
+        <v>0.2876418110555966</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8658211205604626</v>
+        <v>0.4719405879425919</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03397634776255379</v>
+        <v>0.02049438205934407</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4561464499893848</v>
+        <v>0.2248262053035155</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05958293751648178</v>
+        <v>0.03594029158310495</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5413246385635762</v>
+        <v>0.2762054937622342</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07238623239344595</v>
+        <v>0.04366320975871988</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.626508496485877</v>
+        <v>0.3275882019587611</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01915504572958355</v>
+        <v>0.01155418788124789</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.592340267880112</v>
+        <v>0.3069779783840266</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01064200887604561</v>
+        <v>0.006417104351165654</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5944504529066041</v>
+        <v>0.3082488606887963</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02235856484494683</v>
+        <v>0.01348698945083388</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6285410472630153</v>
+        <v>0.3288123602160108</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008781339144401675</v>
+        <v>0.005294658180000239</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6237249299540354</v>
+        <v>0.3259053062485033</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006253064670408886</v>
+        <v>0.003769158075759273</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.627444847586104</v>
+        <v>0.3281472705010839</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002458214634705909</v>
+        <v>0.001480532971537081</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6261033416632992</v>
+        <v>0.3273358735346063</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001393061742477589</v>
+        <v>0.0008381530023541796</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.626429815179107</v>
+        <v>0.3275309646785506</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005269892614988199</v>
+        <v>0.0003167771692067918</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.626090789482306</v>
+        <v>0.3273241493362637</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002449180206554711</v>
+        <v>0.0001458315807480156</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6260520826430719</v>
+        <v>0.3272988064421003</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.62277582619991e-05</v>
+        <v>4.989812001607026e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6259802183895116</v>
+        <v>0.3272534524713112</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.218818784456313e-05</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6259374719923048</v>
+        <v>0.3272256063400598</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.355601046452064e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6259324511423277</v>
+        <v>0.3272205936811452</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6259285058062275</v>
+        <v>0.3272162480553358</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6259262548784958</v>
+        <v>0.3272128977005431</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6259206632184875</v>
+        <v>0.3272075283735553</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6259143392244796</v>
+        <v>0.3272015356401249</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6259089714359013</v>
+        <v>0.3271961678515465</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.625909008184393</v>
+        <v>0.3271962046000382</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6259091184298685</v>
+        <v>0.3271963148455138</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6259091919268521</v>
+        <v>0.3271963883424974</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6259093756693113</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6259109191059677</v>
+        <v>0.327198115521613</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6259123890456408</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6259136384943628</v>
+        <v>0.3272008349100081</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6259149981885601</v>
+        <v>0.3272021946042054</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6259127932790508</v>
+        <v>0.3271999896946962</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6259123890456408</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6259115438303289</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6259120950577061</v>
+        <v>0.3271992914733514</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6259117643212797</v>
+        <v>0.327198960736925</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6259114703333453</v>
+        <v>0.3271986667489906</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6259115438303289</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6259111028484269</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6259109926029514</v>
+        <v>0.3271981890185967</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6259109558544597</v>
+        <v>0.327198152270105</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6259111028484269</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6259106251180333</v>
+        <v>0.3271978215336785</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6259115805788206</v>
+        <v>0.3271987769944659</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6259115438303289</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6259112130939024</v>
+        <v>0.3271984095095478</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6259116540758044</v>
+        <v>0.3271988504914497</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6259110293514433</v>
+        <v>0.3271982257670886</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6259108456089841</v>
+        <v>0.3271980420246294</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6259104413755741</v>
+        <v>0.3271976377912194</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6259095961602621</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6259095594117704</v>
+        <v>0.3271967558274158</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6259097064057376</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.625909632908754</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6259097064057376</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6259097431542296</v>
+        <v>0.3271969395698749</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.625909632908754</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.625910073890656</v>
+        <v>0.3271972703063013</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6259099636451805</v>
+        <v>0.3271971600608258</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6259099268966886</v>
+        <v>0.3271971233123338</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.625909853399705</v>
+        <v>0.3271970498153502</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6259098166512133</v>
+        <v>0.3271970130668585</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6259095961602621</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6259095226632785</v>
+        <v>0.3271967190789238</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6259094491662949</v>
+        <v>0.3271966455819402</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6259094859147868</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6259093756693113</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6259094859147868</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6259097799027213</v>
+        <v>0.3271969763183666</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_5_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.713175878173206e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08860957632026108</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.7331981600291557</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-8.310481028154027e-05</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>-0.2935086370894873</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.7331981600291557</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="58">
@@ -47047,17 +47047,17 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.08868670807904284</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="59">
@@ -47842,17 +47842,17 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.0888193256065232</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4768624264230748</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8658211205604626</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03397634776255379</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4561464499893848</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05958293751648178</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5413246385635762</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07238623239344595</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.626508496485877</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01915504572958355</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.592340267880112</v>
+        <v>-0.2935917418997688</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01064200887604561</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5944504529066041</v>
+        <v>-0.2936723737733212</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02235856484494683</v>
+        <v>0.1854148165383122</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6285410472630153</v>
+        <v>0.07755692884274852</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008781339144401675</v>
+        <v>0.0666164414076286</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6237249299540354</v>
+        <v>0.0251359651068137</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006253064670408886</v>
+        <v>0.05360119492944683</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.627444847586104</v>
+        <v>0.06567207898391807</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002458214634705909</v>
+        <v>0.01955261169208915</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6261033416632992</v>
+        <v>0.0511108084773086</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001393061742477589</v>
+        <v>0.01158871538494977</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.626429815179107</v>
+        <v>0.05471510554689961</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005269892614988199</v>
+        <v>0.003979394734888472</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.626090789482306</v>
+        <v>0.05107301007167297</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002449180206554711</v>
+        <v>0.001805951071685594</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6260520826430719</v>
+        <v>0.05070139251189725</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.62277582619991e-05</v>
+        <v>0.0005377630241374514</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6259802183895116</v>
+        <v>0.04996912765863328</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.218818784456313e-05</v>
+        <v>6.256201422592789e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.204705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6259374719923048</v>
+        <v>0.04955520872788248</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.355601046452064e-06</v>
+        <v>2.883575752967863e-05</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6259324511423277</v>
+        <v>0.04954997863349225</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>1.751560496757181e-05</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6259285058062275</v>
+        <v>0.04955621245147009</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>2.038899403240425e-05</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6259262548784958</v>
+        <v>0.04957961482183216</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>4.996417910458708e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6259206632184875</v>
+        <v>0.04956884613675042</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-7.8868242546452e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6259143392244796</v>
+        <v>0.04955092697422812</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6259089714359013</v>
+        <v>0.04945461293744947</v>
       </c>
     </row>
     <row r="81">
@@ -65328,7 +65328,7 @@
         <v>0</v>
       </c>
       <c r="IY81" t="n">
-        <v>0</v>
+        <v>0.01382146572888683</v>
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.625909008184393</v>
+        <v>0.07726303238454997</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0</v>
+        <v>0.02785963775584339</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6259091184298685</v>
+        <v>0.1191096973555898</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0</v>
+        <v>0.02091278717505507</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6259091919268521</v>
+        <v>0.1330290995427677</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0</v>
+        <v>0.0191853055826866</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6259093756693113</v>
+        <v>0.1504660221299934</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0</v>
+        <v>0.04625264944717573</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6259109191059677</v>
+        <v>0.223819581841849</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0</v>
+        <v>0.04058356199957586</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6259123890456408</v>
+        <v>0.2587224884784478</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0</v>
+        <v>0.02771110684208283</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6259136384943628</v>
+        <v>0.2735407911978543</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0</v>
+        <v>0.01789554820759104</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6259149981885601</v>
+        <v>0.2816002380841114</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0</v>
+        <v>0.005670809523896687</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6259127932790508</v>
+        <v>0.2750305659636811</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0</v>
+        <v>0.00253101127614884</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6259123890456408</v>
+        <v>0.2744211981226068</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0</v>
+        <v>0.0009506694486262552</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6259115438303289</v>
+        <v>0.2737860966520887</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0</v>
+        <v>0.000575239982548569</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6259120950577061</v>
+        <v>0.2739853995632883</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>0</v>
+        <v>0.0002543984138036521</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6259117643212797</v>
+        <v>0.2739185426615756</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>0</v>
+        <v>0.0001097973749169883</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6259114703333453</v>
+        <v>0.2738860498761539</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>0</v>
+        <v>5.408708956560179e-05</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6259115438303289</v>
+        <v>0.273884426252116</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>0</v>
+        <v>2.054261404675963e-05</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6259111028484269</v>
+        <v>0.2738688083502089</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>0</v>
+        <v>7.110627937989877e-06</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6259109926029514</v>
+        <v>0.2738624690301397</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>0</v>
+        <v>9.452007880966109e-07</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6259109558544597</v>
+        <v>0.2738572404843017</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>0</v>
+        <v>-2.871448829436698e-06</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6259111028484269</v>
+        <v>0.2738526786048482</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>0</v>
+        <v>-3.348605946662769e-06</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6259106251180333</v>
+        <v>0.2738467208559823</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6259115805788206</v>
+        <v>0.2738476763167695</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.602580650042519</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6259115438303289</v>
+        <v>0.2738476395682778</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6259112130939024</v>
+        <v>0.2738473088318515</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6259116540758044</v>
+        <v>0.2738477498137534</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.804705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6259110293514433</v>
+        <v>0.2738471250893923</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6259108456089841</v>
+        <v>0.2738469413469332</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6259104413755741</v>
+        <v>0.2738465371135231</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6259095961602621</v>
+        <v>0.2738456918982111</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6259095594117704</v>
+        <v>0.2738456551497194</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6259097064057376</v>
+        <v>0.2738458021436867</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.625909632908754</v>
+        <v>0.2738457286467031</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.204705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6259097064057376</v>
+        <v>0.2738458021436867</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6259097431542296</v>
+        <v>0.2738458388921786</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.625909632908754</v>
+        <v>0.2738457286467031</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.625910073890656</v>
+        <v>0.273846169628605</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6259099636451805</v>
+        <v>0.2738460593831294</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6259099268966886</v>
+        <v>0.2738460226346375</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.625909853399705</v>
+        <v>0.2738459491376539</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6259098166512133</v>
+        <v>0.2738459123891622</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6259095961602621</v>
+        <v>0.2738456918982111</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6259095226632785</v>
+        <v>0.2738456184012275</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6259094491662949</v>
+        <v>0.2738455449042439</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6259094859147868</v>
+        <v>0.2738455816527358</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6259093756693113</v>
+        <v>0.2738454714072603</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6259094859147868</v>
+        <v>0.2738455816527358</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.082561524747701e-06</v>
+        <v>-4.192807000216586e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6259097799027213</v>
+        <v>0.2738458756406703</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_5_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.1985145807266235</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.1058089956641197</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.04030671343207359</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.191797874516439</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.002766810357570648</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.02971328049898148</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.09153281518062423</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.03896767646074295</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.03406526148319244</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.03524969518184662</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.02982296049594879</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.03153511136770248</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.02862518280744553</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.02970624715089798</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.03015640377998352</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.03158154338598251</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.02582178264856339</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.03424018621444702</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.04011701047420502</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.04163642972707748</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.04190597683191299</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.04073788225650787</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.04270164668560028</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.0405694842338562</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.04125743359327316</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.03731480985879898</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.04110957682132721</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.04212510585784912</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.04383467137813568</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.04173144698143005</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.03871303051710129</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.03629327565431595</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.01610235124826431</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.03072226047515869</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.03516820818185806</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.03473601490259171</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.04111374169588089</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.03612123429775238</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.03861185163259506</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.03953869640827179</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.03201453387737274</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.02478723973035812</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.02253513783216476</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.01594392955303192</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.09153281518062423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>7.494911551475525e-05</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.09153281518062423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.009582109749317169</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.09153281518062423</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>-0.0001196160965063609</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.1374159204966616</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0336296409368515</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7331981600291557</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-8.310481028154027e-05</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>-0.2935086370894873</v>
+        <v>0</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.01877420023083687</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7331981600291557</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.02296927571296692</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.16</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01890851184725761</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01876044645905495</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01642977818846703</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01823066174983978</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01336565613746643</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01549093797802925</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.01492175459861755</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01466790959239006</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01432142779231071</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="58">
@@ -47047,17 +47047,17 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.008893251419067383</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.09153281518062423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="59">
@@ -47842,17 +47842,17 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.006402388215065002</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.09153281518062423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.2935917418997688</v>
+        <v>-0.1376435385993759</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>0.3883506178815589</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.009482908993959427</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.09153281518062423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.2935917418997688</v>
+        <v>0.6398033445709872</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>0.02766989998754913</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.004057008773088455</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.09153281518062423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.2935917418997688</v>
+        <v>0.306169569647504</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>0.04852357685903087</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.008761659264564514</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.09153281518062423</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.2935917418997688</v>
+        <v>0.3755375892898636</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>0.05895010350823814</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.002440854907035828</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.09153281518062423</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.2935917418997688</v>
+        <v>0.4449102265519465</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>0.01559967439475466</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.007578812539577484</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.09153281518062423</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.2935917418997688</v>
+        <v>0.4170839141715721</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>0.008665666337357844</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.02086810395121574</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5501325296679072</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.2936723737733212</v>
+        <v>0.4188015064114707</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.1854148165383122</v>
+        <v>0.0182089015005332</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01343428716063499</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.191797874516439</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.07755692884274852</v>
+        <v>0.4465652362769251</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.0666164414076286</v>
+        <v>0.007151234046074364</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01146486960351467</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.191797874516439</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.0251359651068137</v>
+        <v>0.4426419815757233</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.05360119492944683</v>
+        <v>0.005090458389302052</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0006369985640048981</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.191797874516439</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.06567207898391807</v>
+        <v>0.4456704085918553</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.01955261169208915</v>
+        <v>0.002000605300694944</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01477640122175217</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.0511108084773086</v>
+        <v>0.4445768276295488</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.01158871538494977</v>
+        <v>0.001134104330419998</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01583430171012878</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.191797874516439</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.05471510554689961</v>
+        <v>0.4448419036253393</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.003979394734888472</v>
+        <v>0.0004283422461215553</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.02099498175084591</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.191797874516439</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.05107301007167297</v>
+        <v>0.4445647483254433</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.001805951071685594</v>
+        <v>0.0001986776820319919</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.02056990563869476</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.191797874516439</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.05070139251189725</v>
+        <v>0.4445322779939091</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>0.0005377630241374514</v>
+        <v>6.927392708056564e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.02019621804356575</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.191797874516439</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.04996912765863328</v>
+        <v>0.444472785205642</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>6.256201422592789e-05</v>
+        <v>1.69413445763141e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.02190284989774227</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.191797874516439</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.04955520872788248</v>
+        <v>0.4444369924644523</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>2.883575752967863e-05</v>
+        <v>5.970672288157051e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.01534388959407806</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.04954997863349225</v>
+        <v>0.4444319753376853</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.751560496757181e-05</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.01427153870463371</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.04955621245147009</v>
+        <v>0.4444278478366064</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>2.038899403240425e-05</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.004066526889801025</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.3501325296679072</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.04957961482183216</v>
+        <v>0.4444250466907287</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>4.996417910458708e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003258302807807922</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.04956884613675042</v>
+        <v>0.4444196029457224</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-7.8868242546452e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.004699144512414932</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.04955092697422812</v>
+        <v>0.444413610212292</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.0001719221472740173</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.04945461293744947</v>
+        <v>0.4444082424237137</v>
       </c>
     </row>
     <row r="81">
@@ -65328,7 +65328,7 @@
         <v>0</v>
       </c>
       <c r="IY81" t="n">
-        <v>0.01382146572888683</v>
+        <v>0</v>
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002618644386529922</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.07726303238454997</v>
+        <v>0.4444082791722054</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.02785963775584339</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002017132937908173</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1191096973555898</v>
+        <v>0.4444083894176809</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.02091278717505507</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.004202153533697128</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1330290995427677</v>
+        <v>0.4444084629146645</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.0191853055826866</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01288679242134094</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3501325296679072</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1504660221299934</v>
+        <v>0.4444086466571237</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.04625264944717573</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01506267860531807</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.191797874516439</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.223819581841849</v>
+        <v>0.4444101900937802</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.04058356199957586</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0002914518117904663</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.5501325296679072</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2587224884784478</v>
+        <v>0.4444116600334533</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.02771110684208283</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.0006020143628120422</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.09153281518062423</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2735407911978543</v>
+        <v>0.4444129094821753</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.01789554820759104</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.02107076346874237</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2816002380841114</v>
+        <v>0.4444142691763726</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.005670809523896687</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.05297744274139404</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2750305659636811</v>
+        <v>0.4444120642668633</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.00253101127614884</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.04222605377435684</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2744211981226068</v>
+        <v>0.4444116600334533</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.0009506694486262552</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.008215595036745071</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2737860966520887</v>
+        <v>0.4444108148181413</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0.000575239982548569</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.006088152527809143</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.3501325296679072</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2739853995632883</v>
+        <v>0.4444113660455186</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>0.0002543984138036521</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.02640171721577644</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.191797874516439</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2739185426615756</v>
+        <v>0.4444110353090922</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>0.0001097973749169883</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.04589324444532394</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2738860498761539</v>
+        <v>0.4444107413211577</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>5.408708956560179e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.04629150405526161</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.273884426252116</v>
+        <v>0.4444108148181413</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>2.054261404675963e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.05454113334417343</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2738688083502089</v>
+        <v>0.4444103738362393</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>7.110627937989877e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.05538333207368851</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2738624690301397</v>
+        <v>0.4444102635907638</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>9.452007880966109e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.05442037805914879</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2738572404843017</v>
+        <v>0.4444102268422721</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>-2.871448829436698e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.04027396067976952</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.191797874516439</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2738526786048482</v>
+        <v>0.4444103738362393</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>-3.348605946662769e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.05173686891794205</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.191797874516439</v>
+        <v>-0.16</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2738467208559823</v>
+        <v>0.4444098961058457</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.02510113082826138</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.3501325296679072</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2738476763167695</v>
+        <v>0.444410851566633</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.003747504204511642</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3501325296679072</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2738476395682778</v>
+        <v>0.4444108148181413</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.006641045212745667</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3501325296679072</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2738473088318515</v>
+        <v>0.4444104840817149</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.0148028526455164</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2738477498137534</v>
+        <v>0.4444109250636168</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.03098113462328911</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.16</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2738471250893923</v>
+        <v>0.4444103003392557</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.0422552153468132</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.191797874516439</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2738469413469332</v>
+        <v>0.4444101165967965</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.04355704784393311</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2738465371135231</v>
+        <v>0.4444097123633865</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.05049272254109383</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2738456918982111</v>
+        <v>0.4444088671480745</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.04841911792755127</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2738456551497194</v>
+        <v>0.4444088303995828</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.03277850151062012</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.191797874516439</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2738458021436867</v>
+        <v>0.4444089773935501</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.02279582805931568</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.191797874516439</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2738457286467031</v>
+        <v>0.4444089038965665</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.02843879535794258</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.191797874516439</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2738458021436867</v>
+        <v>0.4444089773935501</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.01222160831093788</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2738458388921786</v>
+        <v>0.444409014142042</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.01893829368054867</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2738457286467031</v>
+        <v>0.4444089038965665</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.008742779493331909</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.273846169628605</v>
+        <v>0.4444093448784684</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.01112478971481323</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2738460593831294</v>
+        <v>0.4444092346329929</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01081953570246696</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2738460226346375</v>
+        <v>0.444409197884501</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.0123242475092411</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2738459491376539</v>
+        <v>0.4444091243875173</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01089921034872532</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2738459123891622</v>
+        <v>0.4444090876390256</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.008317440748214722</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2738456918982111</v>
+        <v>0.4444088671480745</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.01249623112380505</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2738456184012275</v>
+        <v>0.4444087936510909</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.009424297139048576</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2738455449042439</v>
+        <v>0.4444087201541073</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.003637772053480148</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2738455816527358</v>
+        <v>0.4444087569025992</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.006766367703676224</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2738454714072603</v>
+        <v>0.4444086466571237</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.01762891560792923</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2738455816527358</v>
+        <v>0.4444087569025992</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.192807000216586e-06</v>
+        <v>-4.082561524747701e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.01723372377455235</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.3999999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2738458756406703</v>
+        <v>0.4444090508905337</v>
       </c>
     </row>
   </sheetData>
